--- a/ig/ch-term/ValueSet-ch-vacd-targetdiseasesandillnessesundergoneforimmunization-vs.xlsx
+++ b/ig/ch-term/ValueSet-ch-vacd-targetdiseasesandillnessesundergoneforimmunization-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="172">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T10:47:47+00:00</t>
+    <t>2026-06-10T10:00:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -514,6 +514,12 @@
   </si>
   <si>
     <t>RhD negative (finding)</t>
+  </si>
+  <si>
+    <t>111864006</t>
+  </si>
+  <si>
+    <t>Chikungunya fever (disorder)</t>
   </si>
   <si>
     <t/>
@@ -796,7 +802,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:B72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1360,15 +1366,23 @@
         <v>167</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>169</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
